--- a/02_加值成品/八下/八下4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-3 可逆反應與化學平衡　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下4-3 可逆反應與化學平衡　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>可正逆雙向進行的反應是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>可逆反應</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>不再改變</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>溶解逸出平衡</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>化學平衡</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>雙向</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>可逆反應用什麼符號？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>維持定值</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>動態</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>⇌</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>被打破</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>雙箭號</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>正逆速率相等時達到？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>可逆反應</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>動態</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>化學平衡</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>動態平衡</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>平衡時反應停止了嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>可逆反應</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>沒有</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>化學平衡</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>被打破</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>動態</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>平衡時反應物生成物濃度？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>兩方向抵消</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>可逆反應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>定值</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>不再改變</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>定值</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>平衡是動態還靜態？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>動態</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>動態平衡</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>維持定值</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>持續進行</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>密閉汽水的CO₂處於？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>溶解逸出平衡</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>是(動態)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>⇌</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>動態</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>改變溫度會使平衡？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>可逆反應</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>被打破</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>不再改變</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>化學平衡</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>重新平衡</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>正逆反應速率相等的狀態稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>化學平衡</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>⇌</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>溶解逸出平衡</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>平衡時反應是否仍在進行？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>是(動態)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>動態</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>⇌</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>動態</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-3 可逆反應與化學平衡　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下4-3 可逆反應與化學平衡　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>達平衡的條件是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>正逆反應速率相等</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>兩方向速率相等外觀不變</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>壓力降低平衡右移CO₂大量逸出</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>仍持續但速率相等</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>關鍵</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>平衡時外觀為何無變化？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>化學平衡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>⇌</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>維持定值</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>兩方向抵消</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>速率等</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>可逆反應能100%完成嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>兩方向抵消</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>不再改變</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>⇌</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>有逆反應</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>打開汽水瓶平衡如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>被打破CO₂逸出</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>兩方向速率相等外觀不變</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>前者雙向後者單向</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>正逆反應速率相等</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>改變</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>平衡時濃度維持？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>化學平衡</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>是(動態)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>可逆反應</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>定值</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>動態平衡指反應？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>前者雙向後者單向</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>被打破再達新平衡</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>仍持續但速率相等</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>被打破CO₂逸出</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>動態</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>密閉容器水蒸發凝結達？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>動態平衡</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>動態</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>⇌</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>汽液</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>溫度升高通常使反應速率？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>加快(正逆皆變)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>向吸熱方向移動</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>被打破CO₂逸出</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>壓力降低平衡右移CO₂逸出</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>影響</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>達到平衡時各物質濃度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>維持定值</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>⇌</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>被打破</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>動態</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>定值</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>改變條件後平衡會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>被打破再達新平衡</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>被打破CO₂逸出</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>加快(正逆皆變)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>向吸熱方向移動</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>移動</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-3 可逆反應與化學平衡　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下4-3 可逆反應與化學平衡　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何平衡是動態而非靜止？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>仍持續但速率相等</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>正逆反應持續進行只是速率相等</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>正逆反應速率相等</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>被打破再達新平衡</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>本質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>打開汽水瓶為何冒泡?用平衡解釋？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>加快(正逆皆變)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>仍持續但速率相等</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>壓力降低平衡右移CO₂逸出</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>被打破CO₂逸出</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>移動</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>平衡時正逆速率關係與濃度關係？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>速率相等、濃度定值</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>兩方向速率相等外觀不變</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>可逆平衡調節H⁺</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>加快(正逆皆變)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>特徵</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>若持續移走生成物平衡如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>正反應持續進行</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>被打破CO₂逸出</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>壓力降低平衡右移CO₂大量逸出</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>加快(正逆皆變)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>移動</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>動態平衡與物態變化平衡的共通點？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>壓力降低平衡右移CO₂大量逸出</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>向吸熱方向移動</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>兩方向速率相等外觀不變</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>壓力降低平衡右移CO₂逸出</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>類比</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>可逆反應⇌與不可逆→差別？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>壓力降低平衡右移CO₂大量逸出</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>前者雙向後者單向</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>正逆反應速率相等</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>被打破再達新平衡</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>符號</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>提高溫度可能使平衡?(定性)</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>正反應持續進行</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>正逆反應持續進行只是速率相等</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>正逆反應速率相等</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>向吸熱方向移動</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>移動</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>血液緩衝維持pH靠什麼原理？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>加快(正逆皆變)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>被打破CO₂逸出</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>可逆平衡調節H⁺</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>壓力降低平衡右移CO₂逸出</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>搖晃汽水後開瓶噴發用平衡解釋？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>仍持續但速率相等</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>壓力降低平衡右移CO₂大量逸出</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>前者雙向後者單向</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>加快(正逆皆變)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>移動</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>密閉容器內水的蒸發與凝結達到？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>可逆反應</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>動態平衡</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不再改變</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>兩方向抵消</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>汽液平衡</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>雙向</t>
+          <t>雙向：這種反應不只能從反應物變成生成物，生成物也能反過來變回反應物</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>雙箭號</t>
+          <t>雙箭號：這個符號有兩個方向的箭頭，代表反應可以正著走也可以逆著走</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：當往前變成生成物的速度和往回變成反應物的速度一樣快時，就達到了化學平衡</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>動態：達到平衡並不代表反應停下來，正反應和逆反應其實都還在持續進行</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>定值</t>
+          <t>定值：雖然反應仍在進行，但因為兩個方向速率相等，濃度看起來就固定不再變動</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>持續進行</t>
+          <t>持續進行：平衡狀態下反應物和生成物一直在互相轉換，只是轉換的速率剛好相等而已</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>動態：瓶內二氧化碳溶進水裡的速度和從水中跑出來的速度相等，達到一種動態平衡</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>重新平衡</t>
+          <t>重新平衡：改變溫度會讓正逆反應的速率不再相等，原本的平衡會被打破，之後再建立新的平衡</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：當正反應和逆反應的速率相等時，反應物與生成物的濃度不再改變，這種狀態稱為化學平衡</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>動態：達到化學平衡並不代表反應停止了，正反應和逆反應其實都還在持續進行，只是速率相等，所以是一種動態平衡</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>關鍵</t>
+          <t>關鍵：只要正反應和逆反應進行的速率剛好一樣快，系統就會達到平衡狀態</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>速率等</t>
+          <t>速率等：因為往前和往回轉變的量剛好互相抵消，所以從外表看起來好像沒有任何變化在發生</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>有逆反應</t>
+          <t>有逆反應：因為生成物又會反過來變回反應物，所以可逆反應永遠不會把反應物全部用完</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>改變</t>
+          <t>改變：瓶蓋打開後壓力降低，讓溶解在水裡的二氧化碳開始大量跑出來，原本的平衡狀態被打破了</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>不變：達到平衡之後，反應物和生成物的濃度會停留在某個固定的數值，不會再繼續改變</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>動態：反應本身其實沒有停止，只是正逆兩個方向進行的速度剛好相等，外觀才顯得沒有變化</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>汽液</t>
+          <t>汽液：水分子變成水蒸氣的速度和水蒸氣變回水的速度相等時，就達到了汽液間的動態平衡</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>影響：溫度升高會讓粒子動能變大，正反應和逆反應的速率通常都會跟著加快</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>定值</t>
+          <t>定值：達到化學平衡後，只要外界條件不變，反應物和生成物的濃度會維持在固定數值，不再隨時間改變</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>移動</t>
+          <t>移動：當溫度、濃度或壓力等條件改變時，原本的平衡狀態會被打破，反應會朝某個方向移動，直到建立起新的平衡</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>本質</t>
+          <t>本質：反應物和生成物其實一直在互相轉換，只是雙向的速率剛好相等，才會看起來像是靜止不動</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>移動</t>
+          <t>移動：打開瓶蓋讓瓶內壓力下降，使溶解的平衡往釋放氣體的方向移動，於是二氧化碳大量逸出冒泡</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>特徵</t>
+          <t>特徵：平衡狀態的兩個重要特徵是正逆反應速率相等，以及各物質濃度維持在固定的數值</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>移動</t>
+          <t>移動：不斷把生成物拿走會讓逆反應的機會變少，使反應持續往生成更多產物的方向進行</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>類比</t>
+          <t>類比：不管是化學反應的平衡還是水和水蒸氣間的平衡，都是兩個方向的速率相等，看起來才沒有變化</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>符號</t>
+          <t>符號：雙箭頭代表反應可以雙向進行，單箭頭則代表反應只能往一個方向走到底，不會逆轉</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>移動</t>
+          <t>移動：溫度升高時系統會傾向往需要吸收熱量的那個方向移動，以緩和溫度上升的影響</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：血液中的緩衝物質能透過可逆反應的平衡移動，隨時吸收或釋放氫離子，維持穩定的酸鹼度</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>移動</t>
+          <t>移動：汽水中的二氧化碳原本和水維持一種溶解平衡，搖晃後開瓶壓力瞬間降低，平衡往釋放氣體的方向移動，使大量二氧化碳快速逸出，造成噴發</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>汽液平衡</t>
+          <t>汽液平衡：密閉容器中水持續蒸發成水蒸氣，同時水蒸氣也持續凝結回水，當兩者速率相等時，就達到了汽液間的動態平衡</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-3_三種難度測驗卷.xlsx
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>維持定值</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>動態平衡</t>
-        </is>
-      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>維持定值</t>
+          <t>溶解逸出平衡</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>定值</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>可逆反應</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>⇌</t>
+          <t>被打破</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>化學平衡</t>
+          <t>不再改變</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>是(動態)</t>
+          <t>動態</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>可逆反應</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>沒有</t>
+          <t>可逆反應</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>⇌</t>
+          <t>不再改變</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>⇌</t>
+          <t>可逆反應</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>被打破</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>化學平衡</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>可逆反應</t>
+          <t>⇌</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>兩方向抵消</t>
+          <t>溶解逸出平衡</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
